--- a/IPC.xlsx
+++ b/IPC.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://farmacity.sharepoint.com/sites/PerformanceEficiencia/Shared Documents/2025/Automatización/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://farmacity.sharepoint.com/sites/PerformanceEficiencia/Shared Documents/2025/Automatización/Tablero CAPEX/app ajuste roi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="137" documentId="13_ncr:1_{58C70089-FDDF-4DDD-8F55-2AFFFFA42B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B21975A-4CC7-4FFF-BE4C-1202FC05B71C}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="13_ncr:1_{58C70089-FDDF-4DDD-8F55-2AFFFFA42B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{472EE50A-2208-421B-AFB6-BA6064D56FB1}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B117CEED-1A99-47C6-982B-3272E3DCE7F9}"/>
   </bookViews>
@@ -235,7 +235,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -272,6 +272,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -1096,6 +1097,18 @@
       <c r="AM2" s="16">
         <v>2.9000000000000001E-2</v>
       </c>
+      <c r="AN2" s="22">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="AO2" s="22"/>
+      <c r="AP2" s="16"/>
+      <c r="AQ2" s="16"/>
+      <c r="AR2" s="22"/>
+      <c r="AS2" s="22"/>
+      <c r="AT2" s="16"/>
+      <c r="AU2" s="16"/>
+      <c r="AV2" s="22"/>
+      <c r="AW2" s="22"/>
     </row>
     <row r="3" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
@@ -1217,6 +1230,19 @@
         <f t="shared" si="1"/>
         <v>0.33099887232482139</v>
       </c>
+      <c r="AN3" s="10">
+        <f t="shared" ref="AN3" si="2">+(1+AN2)*(1+AM2)*(1+AL2)*(1+AK2)*(1+AJ2)*(1+AI2)*(1+AH2)*(1+AG2)*(1+AF2)*(1+AE2)*(1+AD2)*(1+AC2)-1</f>
+        <v>0.32676451748179369</v>
+      </c>
+      <c r="AO3" s="10"/>
+      <c r="AP3" s="10"/>
+      <c r="AQ3" s="10"/>
+      <c r="AR3" s="10"/>
+      <c r="AS3" s="10"/>
+      <c r="AT3" s="10"/>
+      <c r="AU3" s="10"/>
+      <c r="AV3" s="10"/>
+      <c r="AW3" s="10"/>
     </row>
     <row r="4" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
@@ -1243,43 +1269,43 @@
         <v>0.36519200000000018</v>
       </c>
       <c r="P4" s="6">
-        <f t="shared" ref="P4:Y4" si="2">+(1+O4)*(1+P2)-1</f>
+        <f t="shared" ref="P4:Y4" si="3">+(1+O4)*(1+P2)-1</f>
         <v>0.5153631200000004</v>
       </c>
       <c r="Q4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.64871507456000055</v>
       </c>
       <c r="R4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.71796110769152066</v>
       </c>
       <c r="S4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.79698731864533068</v>
       </c>
       <c r="T4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.86886681139114397</v>
       </c>
       <c r="U4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.94735921746957219</v>
       </c>
       <c r="V4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.0155167900810071</v>
       </c>
       <c r="W4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.0699357434131942</v>
       </c>
       <c r="X4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.1196142012551107</v>
       </c>
       <c r="Y4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.1768437846889985</v>
       </c>
       <c r="Z4" s="11">
@@ -1287,47 +1313,47 @@
         <v>2.2100000000000009E-2</v>
       </c>
       <c r="AA4" s="11">
-        <f t="shared" ref="AA4:AF4" si="3">+(1+AA2)*(1+Z4)-1</f>
+        <f t="shared" ref="AA4:AF4" si="4">+(1+AA2)*(1+Z4)-1</f>
         <v>4.6630399999999961E-2</v>
       </c>
       <c r="AB4" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.5669713920000001E-2</v>
       </c>
       <c r="AC4" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.11585133196697606</v>
       </c>
       <c r="AD4" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.13258910194648066</v>
       </c>
       <c r="AE4" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.15093704539801367</v>
       </c>
       <c r="AF4" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.17280484926057582</v>
       </c>
       <c r="AG4" s="11">
-        <f t="shared" ref="AG4:AK4" si="4">+(1+AG2)*(1+AF4)-1</f>
+        <f t="shared" ref="AG4:AL4" si="5">+(1+AG2)*(1+AF4)-1</f>
         <v>0.19485358042667467</v>
       </c>
       <c r="AH4" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.2197065348995495</v>
       </c>
       <c r="AI4" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.24824766781619911</v>
       </c>
       <c r="AJ4" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.27945385951160406</v>
       </c>
       <c r="AK4" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.31590549996908956</v>
       </c>
       <c r="AL4" s="11">
@@ -1335,9 +1361,22 @@
         <v>2.8799999999999937E-2</v>
       </c>
       <c r="AM4" s="11">
-        <f>+(1+AM2)-1</f>
-        <v>2.8999999999999915E-2</v>
-      </c>
+        <f t="shared" ref="AM4" si="6">+(1+AM2)*(1+AL4)-1</f>
+        <v>5.8635199999999887E-2</v>
+      </c>
+      <c r="AN4" s="11">
+        <f t="shared" ref="AN4" si="7">+(1+AN2)*(1+AM4)-1</f>
+        <v>9.4628796799999915E-2</v>
+      </c>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
     </row>
     <row r="5" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1594,148 +1633,156 @@
         <v>106.60000000000001</v>
       </c>
       <c r="D8" s="13">
-        <f t="shared" ref="D8:AM8" si="5">+C8*(1+D2)</f>
+        <f t="shared" ref="D8:AM8" si="8">+C8*(1+D2)</f>
         <v>114.8082</v>
       </c>
       <c r="E8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>124.45208880000001</v>
       </c>
       <c r="F8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>134.15935172640002</v>
       </c>
       <c r="G8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>142.20891282998403</v>
       </c>
       <c r="H8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>151.16807433827302</v>
       </c>
       <c r="I8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>169.91291555621888</v>
       </c>
       <c r="J8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>191.49185583185869</v>
       </c>
       <c r="K8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>207.38567986590294</v>
       </c>
       <c r="L8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>233.93104688873854</v>
       </c>
       <c r="M8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>293.58346384536685</v>
       </c>
       <c r="N8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>354.06165739751242</v>
       </c>
       <c r="O8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>400.79779617398412</v>
       </c>
       <c r="P8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>444.88555375312239</v>
       </c>
       <c r="Q8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>484.03548248339717</v>
       </c>
       <c r="R8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>504.36497274769988</v>
       </c>
       <c r="S8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>527.56576149409409</v>
       </c>
       <c r="T8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>548.66839195385785</v>
       </c>
       <c r="U8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>571.71246441591995</v>
       </c>
       <c r="V8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>591.7224006704771</v>
       </c>
       <c r="W8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>607.69890548857995</v>
       </c>
       <c r="X8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>622.28367922030588</v>
       </c>
       <c r="Y8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>639.08533855925407</v>
       </c>
       <c r="Z8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>653.20912454141364</v>
       </c>
       <c r="AA8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>668.88614353040759</v>
       </c>
       <c r="AB8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>693.83559668409191</v>
       </c>
       <c r="AC8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>713.12422627190972</v>
       </c>
       <c r="AD8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>723.82108966598832</v>
       </c>
       <c r="AE8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>735.54699131857728</v>
       </c>
       <c r="AF8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>749.52238415363013</v>
       </c>
       <c r="AG8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>763.61340497571837</v>
       </c>
       <c r="AH8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>779.49656379921328</v>
       </c>
       <c r="AI8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>797.73678339211494</v>
       </c>
       <c r="AJ8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>817.68020297691771</v>
       </c>
       <c r="AK8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>840.97591195973007</v>
       </c>
       <c r="AL8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>865.19601822417019</v>
       </c>
       <c r="AM8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>890.28670275267109</v>
+      </c>
+      <c r="AN8" s="13">
+        <f t="shared" ref="AN8" si="9">+AM8*(1+AN2)</f>
+        <v>920.55645064626196</v>
+      </c>
+      <c r="AO8" s="13">
+        <f t="shared" ref="AO8" si="10">+AN8*(1+AO2)</f>
+        <v>920.55645064626196</v>
       </c>
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.3">
@@ -1747,95 +1794,95 @@
         <v>100</v>
       </c>
       <c r="C9" s="14">
-        <f t="shared" ref="C9:Y9" si="6">+C8</f>
+        <f t="shared" ref="C9:Y9" si="11">+C8</f>
         <v>106.60000000000001</v>
       </c>
       <c r="D9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>114.8082</v>
       </c>
       <c r="E9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>124.45208880000001</v>
       </c>
       <c r="F9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>134.15935172640002</v>
       </c>
       <c r="G9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>142.20891282998403</v>
       </c>
       <c r="H9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>151.16807433827302</v>
       </c>
       <c r="I9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>169.91291555621888</v>
       </c>
       <c r="J9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>191.49185583185869</v>
       </c>
       <c r="K9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>207.38567986590294</v>
       </c>
       <c r="L9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>233.93104688873854</v>
       </c>
       <c r="M9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>293.58346384536685</v>
       </c>
       <c r="N9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>354.06165739751242</v>
       </c>
       <c r="O9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>400.79779617398412</v>
       </c>
       <c r="P9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>444.88555375312239</v>
       </c>
       <c r="Q9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>484.03548248339717</v>
       </c>
       <c r="R9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>504.36497274769988</v>
       </c>
       <c r="S9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>527.56576149409409</v>
       </c>
       <c r="T9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>548.66839195385785</v>
       </c>
       <c r="U9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>571.71246441591995</v>
       </c>
       <c r="V9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>591.7224006704771</v>
       </c>
       <c r="W9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>607.69890548857995</v>
       </c>
       <c r="X9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>622.28367922030588</v>
       </c>
       <c r="Y9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>639.08533855925407</v>
       </c>
       <c r="Z9" s="13">
@@ -1843,56 +1890,64 @@
         <v>654.50436747979552</v>
       </c>
       <c r="AA9" s="13">
-        <f t="shared" ref="AA9:AM9" si="7">+Z9*(1+AA5)</f>
+        <f t="shared" ref="AA9:AM9" si="12">+Z9*(1+AA5)</f>
         <v>668.64943532072607</v>
       </c>
       <c r="AB9" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>685.26273801348555</v>
       </c>
       <c r="AC9" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>700.69732093859261</v>
       </c>
       <c r="AD9" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>715.88056493651015</v>
       </c>
       <c r="AE9" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>730.30397197420007</v>
       </c>
       <c r="AF9" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>742.45388060106745</v>
       </c>
       <c r="AG9" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>754.41141117186032</v>
       </c>
       <c r="AH9" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>765.64536593237221</v>
       </c>
       <c r="AI9" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>776.45654770481667</v>
       </c>
       <c r="AJ9" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>786.95286561584999</v>
       </c>
       <c r="AK9" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>799.03978646645885</v>
       </c>
       <c r="AL9" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>816.97303606530363</v>
       </c>
       <c r="AM9" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>833.19349900376949</v>
+      </c>
+      <c r="AN9" s="13">
+        <f t="shared" ref="AN9" si="13">+AM9*(1+AN5)</f>
+        <v>851.99598289303549</v>
+      </c>
+      <c r="AO9" s="13">
+        <f t="shared" ref="AO9" si="14">+AN9*(1+AO5)</f>
+        <v>867.76502604904215</v>
       </c>
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.3">
@@ -3493,19 +3548,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="dd3ed0ad-465b-4b94-9e03-9fde07fe233a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="12e925e7-9bc7-4479-8e5e-5ed9012e158e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D20E8A0A3F7A044EAC1D8300FB25DCEE" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="b6f4662f562d642dfd3a8d1b2eef661d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dd3ed0ad-465b-4b94-9e03-9fde07fe233a" xmlns:ns3="12e925e7-9bc7-4479-8e5e-5ed9012e158e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cad4c00e8c9cd65870f83d4d51d1ea07" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D20E8A0A3F7A044EAC1D8300FB25DCEE" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="73702fa23d3410e8aedc2854b133fdd8">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dd3ed0ad-465b-4b94-9e03-9fde07fe233a" xmlns:ns3="12e925e7-9bc7-4479-8e5e-5ed9012e158e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="29d7ad22752d16cb4316e7690fb516c1" ns2:_="" ns3:_="">
     <xsd:import namespace="dd3ed0ad-465b-4b94-9e03-9fde07fe233a"/>
     <xsd:import namespace="12e925e7-9bc7-4479-8e5e-5ed9012e158e"/>
     <xsd:element name="properties">
@@ -3572,7 +3616,7 @@
         <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4e43bcf6-9966-4633-aac5-578b9509267a" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4e43bcf6-9966-4633-aac5-578b9509267a" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -3595,7 +3639,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="12e925e7-9bc7-4479-8e5e-5ed9012e158e" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="15" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="15" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -3614,7 +3658,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="16" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="16" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -3642,8 +3686,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -3732,6 +3776,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="dd3ed0ad-465b-4b94-9e03-9fde07fe233a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="12e925e7-9bc7-4479-8e5e-5ed9012e158e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3742,6 +3797,10 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B3155F2-060D-48C0-AE23-D24D9B3AA2C6}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6571B10-6268-4B6F-AD0A-74EA79A3E4A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3752,10 +3811,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DD71C28-E873-41DD-9A27-57BC3AC9A26C}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8891529D-FF05-405E-9396-D68A841F8ED5}">
   <ds:schemaRefs>

--- a/IPC.xlsx
+++ b/IPC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://farmacity.sharepoint.com/sites/PerformanceEficiencia/Shared Documents/2025/Automatización/Tablero CAPEX/app ajuste roi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="13_ncr:1_{58C70089-FDDF-4DDD-8F55-2AFFFFA42B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{472EE50A-2208-421B-AFB6-BA6064D56FB1}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="13_ncr:1_{58C70089-FDDF-4DDD-8F55-2AFFFFA42B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82F4F393-09A9-4AE2-9579-6438700E6DF1}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B117CEED-1A99-47C6-982B-3272E3DCE7F9}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{B117CEED-1A99-47C6-982B-3272E3DCE7F9}"/>
   </bookViews>
   <sheets>
     <sheet name="IPC" sheetId="1" r:id="rId1"/>
@@ -351,9 +351,6 @@
           <cell r="M2">
             <v>2.3E-2</v>
           </cell>
-          <cell r="R2">
-            <v>2.2566767397666665E-2</v>
-          </cell>
           <cell r="S2">
             <v>1.8508353880333336E-2</v>
           </cell>
@@ -418,15 +415,6 @@
           </cell>
           <cell r="M7">
             <v>1480</v>
-          </cell>
-          <cell r="P7">
-            <v>1488</v>
-          </cell>
-          <cell r="Q7">
-            <v>1517</v>
-          </cell>
-          <cell r="R7">
-            <v>1550</v>
           </cell>
           <cell r="S7">
             <v>1582</v>
@@ -1337,7 +1325,7 @@
         <v>0.17280484926057582</v>
       </c>
       <c r="AG4" s="11">
-        <f t="shared" ref="AG4:AL4" si="5">+(1+AG2)*(1+AF4)-1</f>
+        <f t="shared" ref="AG4:AK4" si="5">+(1+AG2)*(1+AF4)-1</f>
         <v>0.19485358042667467</v>
       </c>
       <c r="AH4" s="11">
@@ -3069,13 +3057,13 @@
       <c r="BI1" s="19">
         <v>45992</v>
       </c>
-      <c r="BJ1" s="20">
+      <c r="BJ1" s="19">
         <v>46023</v>
       </c>
-      <c r="BK1" s="20">
+      <c r="BK1" s="19">
         <v>46054</v>
       </c>
-      <c r="BL1" s="20">
+      <c r="BL1" s="19">
         <v>46082</v>
       </c>
       <c r="BM1" s="20">
@@ -3309,8 +3297,7 @@
         <v>2.8490000000000001E-2</v>
       </c>
       <c r="BL2" s="18">
-        <f>'[1]Resumen Pautas'!R2</f>
-        <v>2.2566767397666665E-2</v>
+        <v>3.3799999999999997E-2</v>
       </c>
       <c r="BM2" s="18">
         <f>'[1]Resumen Pautas'!S2</f>
@@ -3474,16 +3461,13 @@
         <v>1480</v>
       </c>
       <c r="BJ3" s="21">
-        <f>'[1]Resumen Pautas'!P7</f>
-        <v>1488</v>
+        <v>1475</v>
       </c>
       <c r="BK3" s="21">
-        <f>'[1]Resumen Pautas'!Q7</f>
-        <v>1517</v>
+        <v>1420</v>
       </c>
       <c r="BL3" s="21">
-        <f>'[1]Resumen Pautas'!R7</f>
-        <v>1550</v>
+        <v>1400</v>
       </c>
       <c r="BM3" s="21">
         <f>'[1]Resumen Pautas'!S7</f>
@@ -3548,6 +3532,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="dd3ed0ad-465b-4b94-9e03-9fde07fe233a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="12e925e7-9bc7-4479-8e5e-5ed9012e158e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D20E8A0A3F7A044EAC1D8300FB25DCEE" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="73702fa23d3410e8aedc2854b133fdd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dd3ed0ad-465b-4b94-9e03-9fde07fe233a" xmlns:ns3="12e925e7-9bc7-4479-8e5e-5ed9012e158e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="29d7ad22752d16cb4316e7690fb516c1" ns2:_="" ns3:_="">
     <xsd:import namespace="dd3ed0ad-465b-4b94-9e03-9fde07fe233a"/>
@@ -3776,17 +3771,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="dd3ed0ad-465b-4b94-9e03-9fde07fe233a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="12e925e7-9bc7-4479-8e5e-5ed9012e158e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3797,16 +3781,31 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B3155F2-060D-48C0-AE23-D24D9B3AA2C6}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6571B10-6268-4B6F-AD0A-74EA79A3E4A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="dd3ed0ad-465b-4b94-9e03-9fde07fe233a"/>
     <ds:schemaRef ds:uri="12e925e7-9bc7-4479-8e5e-5ed9012e158e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B3155F2-060D-48C0-AE23-D24D9B3AA2C6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="dd3ed0ad-465b-4b94-9e03-9fde07fe233a"/>
+    <ds:schemaRef ds:uri="12e925e7-9bc7-4479-8e5e-5ed9012e158e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/IPC.xlsx
+++ b/IPC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://farmacity.sharepoint.com/sites/PerformanceEficiencia/Shared Documents/2025/Automatización/Tablero CAPEX/app ajuste roi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="13_ncr:1_{58C70089-FDDF-4DDD-8F55-2AFFFFA42B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82F4F393-09A9-4AE2-9579-6438700E6DF1}"/>
+  <xr:revisionPtr revIDLastSave="161" documentId="13_ncr:1_{58C70089-FDDF-4DDD-8F55-2AFFFFA42B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D0E3F6F-84E3-40A6-AB72-BA6859007450}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{B117CEED-1A99-47C6-982B-3272E3DCE7F9}"/>
   </bookViews>
@@ -3294,7 +3294,7 @@
         <v>2.8799999999999999E-2</v>
       </c>
       <c r="BK2" s="18">
-        <v>2.8490000000000001E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="BL2" s="18">
         <v>3.3799999999999997E-2</v>
